--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar15_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar15_Q10_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002762360055300598</v>
+        <v>0.002785203682257616</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002762360055300598</v>
+        <v>0.002785203682257616</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001448451554784598</v>
+        <v>0.001555138335073965</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002740415680080991</v>
+        <v>0.002752998963942188</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002740415680080991</v>
+        <v>0.002752998963942188</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00133622175416825</v>
+        <v>0.00140646966351748</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002696741962168804</v>
+        <v>0.002695370269814491</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002696741962168804</v>
+        <v>0.002695370269814491</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001238567780820674</v>
+        <v>0.001269390851799388</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.002621152855993919</v>
+        <v>0.002604925564023268</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002621152855993919</v>
+        <v>0.002604925564023268</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00114204393705727</v>
+        <v>0.001150824183963075</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.002544059790722</v>
+        <v>0.002515686251555049</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002544059790722</v>
+        <v>0.002515686251555049</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001047447412911189</v>
+        <v>0.001054877496253519</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.002485081271158653</v>
+        <v>0.002449155366319191</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002485081271158653</v>
+        <v>0.002449155366319191</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000959016229022134</v>
+        <v>0.0009748341502486613</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002453106341565834</v>
+        <v>0.002414402924087015</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002453106341565834</v>
+        <v>0.002414402924087015</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0008803245280292992</v>
+        <v>0.0009079290721560118</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002458172222800516</v>
+        <v>0.002421165953593241</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002458172222800516</v>
+        <v>0.002421165953593241</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0008233349536948309</v>
+        <v>0.0008666004010245996</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.002490693733896011</v>
+        <v>0.002459283334805084</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002490693733896011</v>
+        <v>0.002459283334805084</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000796507450527281</v>
+        <v>0.0008648519089444434</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002615634919877478</v>
+        <v>0.00259337074758941</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002615634919877478</v>
+        <v>0.00259337074758941</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0008112842993705765</v>
+        <v>0.0009149219947960531</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002792422790791293</v>
+        <v>0.002782097234914648</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002792422790791293</v>
+        <v>0.002782097234914648</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008564953855283284</v>
+        <v>0.001000260521396168</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003044834429846983</v>
+        <v>0.003048914708191115</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003044834429846983</v>
+        <v>0.003048914708191115</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0009275243212335855</v>
+        <v>0.001103819004783528</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.003392772089677437</v>
+        <v>0.003413579031786455</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003392772089677437</v>
+        <v>0.003413579031786455</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001012676116689046</v>
+        <v>0.001209569814340171</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.003806264907550026</v>
+        <v>0.003844982191982544</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003806264907550026</v>
+        <v>0.003844982191982544</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00110837150586529</v>
+        <v>0.001308457946270574</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00429361587234834</v>
+        <v>0.004350781314220322</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00429361587234834</v>
+        <v>0.004350781314220322</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001219273731744446</v>
+        <v>0.001391932325017725</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00484048933234263</v>
+        <v>0.004915396605945461</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00484048933234263</v>
+        <v>0.004915396605945461</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001361274538550454</v>
+        <v>0.001473309526706646</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.00542254965476012</v>
+        <v>0.005512781789696475</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00542254965476012</v>
+        <v>0.005512781789696475</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001551619659722631</v>
+        <v>0.001582851001974917</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.006049049402333882</v>
+        <v>0.006151239620593691</v>
       </c>
       <c r="C19" t="n">
-        <v>0.006049049402333882</v>
+        <v>0.006151239620593691</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001783064966578466</v>
+        <v>0.001741908155552005</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.006703724690554698</v>
+        <v>0.006813529705340797</v>
       </c>
       <c r="C20" t="n">
-        <v>0.006703724690554698</v>
+        <v>0.006813529705340797</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002019294483863802</v>
+        <v>0.001918528122313644</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.007352787609109804</v>
+        <v>0.007465002491633906</v>
       </c>
       <c r="C21" t="n">
-        <v>0.007352787609109804</v>
+        <v>0.007465002491633906</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002195606104058356</v>
+        <v>0.002056411191156311</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.007981002714887433</v>
+        <v>0.008090948038497421</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007981002714887433</v>
+        <v>0.008090948038497421</v>
       </c>
       <c r="D22" t="n">
-        <v>0.002254838375269528</v>
+        <v>0.00209287335546917</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.008594813976609146</v>
+        <v>0.00869961211607879</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008594813976609146</v>
+        <v>0.00869961211607879</v>
       </c>
       <c r="D23" t="n">
-        <v>0.002185434921387114</v>
+        <v>0.002018095944737041</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.009236257590551966</v>
+        <v>0.009335810191308715</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009236257590551966</v>
+        <v>0.009335810191308715</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0020359527001169</v>
+        <v>0.001892847663231228</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.009936250363268537</v>
+        <v>0.01003385157523929</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009936250363268537</v>
+        <v>0.01003385157523929</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00188494748957908</v>
+        <v>0.001802352735270537</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01072222013426095</v>
+        <v>0.01082329407339157</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01072222013426095</v>
+        <v>0.01082329407339157</v>
       </c>
       <c r="D26" t="n">
-        <v>0.001802616640144406</v>
+        <v>0.001815605163479948</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0115749383760484</v>
+        <v>0.01168485843477087</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0115749383760484</v>
+        <v>0.01168485843477087</v>
       </c>
       <c r="D27" t="n">
-        <v>0.001811395860743649</v>
+        <v>0.001938189618687326</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01248345081606621</v>
+        <v>0.01260810929497429</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01248345081606621</v>
+        <v>0.01260810929497429</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001900932941249414</v>
+        <v>0.002135886268313752</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01341095097403719</v>
+        <v>0.0135546078400673</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01341095097403719</v>
+        <v>0.0135546078400673</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002033592332482838</v>
+        <v>0.002354577792042537</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01431851200386143</v>
+        <v>0.0144830868437569</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01431851200386143</v>
+        <v>0.0144830868437569</v>
       </c>
       <c r="D30" t="n">
-        <v>0.002174991067446109</v>
+        <v>0.002564546884318885</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01520189306132939</v>
+        <v>0.01538820876819236</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01520189306132939</v>
+        <v>0.01538820876819236</v>
       </c>
       <c r="D31" t="n">
-        <v>0.002312640381544727</v>
+        <v>0.002752958640584714</v>
       </c>
     </row>
   </sheetData>
